--- a/results/breakdown/2050/nitrous oxide production, AON 90 cryogenic, green ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 90 cryogenic, green ammonia.xlsx
@@ -446,7 +446,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.2323613555173107</v>
+        <v>0.2323613555173108</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -463,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0004377711620983938</v>
+        <v>0.0004377711620983947</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -480,7 +480,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0003314521939590942</v>
+        <v>0.0003314521939590961</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -497,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.419124032992577E-05</v>
+        <v>1.419124032992576E-05</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.01285745161232085</v>
+        <v>0.01285745161232044</v>
       </c>
       <c r="E7">
         <v>1</v>
